--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -6236,7 +6236,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260412_202446.xlsx
@@ -4554,7 +4554,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
